--- a/data/DNB_OAI.xlsx
+++ b/data/DNB_OAI.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,6 +423,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1043993258</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1056858184</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1185223975</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1195622694</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1380809746</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1387759582</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1389521141</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1394390033</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>139710449X</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1400484057</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1400553415</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1401734650</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1403178364</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1407745875</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1407772376</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/DNB_OAI.xlsx
+++ b/data/DNB_OAI.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,105 +426,679 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1043993258</t>
+          <t>1056856645</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1056858184</t>
+          <t>1077496680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1185223975</t>
+          <t>1185411151</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1195622694</t>
+          <t>1185411534</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1380809746</t>
+          <t>1225638399</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1387759582</t>
+          <t>1231462981</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1389521141</t>
+          <t>1234179199</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1394390033</t>
+          <t>1234603977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>139710449X</t>
+          <t>1242037675</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1400484057</t>
+          <t>1244543691</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1400553415</t>
+          <t>1246104598</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1401734650</t>
+          <t>1246297841</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1403178364</t>
+          <t>1273171268</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1407745875</t>
+          <t>1312198230</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1407772376</t>
+          <t>1324267941</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1325507180</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1350465453</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>136595689X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1369527306</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1370535627</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1372302603</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1378655982</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1380085845</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1380087961</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1380200644</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>138037832X</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1380807964</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1380918774</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1380919436</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1381022200</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1381024106</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1381128106</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1382819188</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1382823045</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1382939191</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1383073589</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1383073899</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1383074445</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1383400075</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1383722749</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1386181110</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1386271535</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>138775971X</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1390103315</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1392634652</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1392743419</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>139320385X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1393219802</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1394007450</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1394328028</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1394983123</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1395398046</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1395398631</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1395399255</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1395518416</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1396364412</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1396365583</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>139650088X</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1396586881</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1397005165</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1397233788</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1397658363</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>139817064X</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1398298093</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1398502723</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1398835250</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1398963054</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1399207539</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1399521926</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1399522000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1399522418</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1400087805</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1400088208</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1400485223</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1400553547</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1401393136</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1401485138</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1401624456</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1401900801</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1401994253</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1402017464</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1402018320</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1402096267</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1402376502</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1402376871</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1402574843</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1402652119</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1403177406</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1403433925</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1404661735</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1406899453</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1406943568</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1408916169</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1408940604</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1409344525</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1409347095</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1409350509</t>
         </is>
       </c>
     </row>

--- a/data/DNB_OAI.xlsx
+++ b/data/DNB_OAI.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,679 +426,4207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1056856645</t>
+          <t>1013571878</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1077496680</t>
+          <t>1015145957</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1185411151</t>
+          <t>1024066177</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1185411534</t>
+          <t>1024070654</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1225638399</t>
+          <t>1024071286</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1231462981</t>
+          <t>1024089959</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1234179199</t>
+          <t>1024091171</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1234603977</t>
+          <t>1024092690</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1242037675</t>
+          <t>1034214837</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1244543691</t>
+          <t>1042398070</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1246104598</t>
+          <t>1043581308</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1246297841</t>
+          <t>1043996338</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1273171268</t>
+          <t>1067044337</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1312198230</t>
+          <t>1072123940</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1324267941</t>
+          <t>1077495749</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1325507180</t>
+          <t>1099953715</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1350465453</t>
+          <t>1102805572</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>136595689X</t>
+          <t>1118501357</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1369527306</t>
+          <t>1160533512</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1370535627</t>
+          <t>117354853X</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1372302603</t>
+          <t>1185714278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1378655982</t>
+          <t>1185714758</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1380085845</t>
+          <t>1186818131</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1380087961</t>
+          <t>1186911743</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1380200644</t>
+          <t>1191634647</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>138037832X</t>
+          <t>1203802226</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1380807964</t>
+          <t>1209449900</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1380918774</t>
+          <t>1209480352</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1380919436</t>
+          <t>1217411208</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1381022200</t>
+          <t>1228449104</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1381024106</t>
+          <t>1228628483</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1381128106</t>
+          <t>1230010866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1382819188</t>
+          <t>1230014624</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1382823045</t>
+          <t>1230065733</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1382939191</t>
+          <t>1230920463</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1383073589</t>
+          <t>1231178531</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1383073899</t>
+          <t>1232258644</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1383074445</t>
+          <t>1232961353</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1383400075</t>
+          <t>1238785921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1383722749</t>
+          <t>123943913X</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1386181110</t>
+          <t>1241677166</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1386271535</t>
+          <t>1242124349</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>138775971X</t>
+          <t>1246771748</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1390103315</t>
+          <t>1292807423</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1392634652</t>
+          <t>131220169X</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1392743419</t>
+          <t>1324875038</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>139320385X</t>
+          <t>132487516X</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1393219802</t>
+          <t>1324875240</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1394007450</t>
+          <t>1325160199</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1394328028</t>
+          <t>1325238341</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1394983123</t>
+          <t>132523995X</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1395398046</t>
+          <t>1325242365</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1395398631</t>
+          <t>1325242659</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1395399255</t>
+          <t>1325242810</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1395518416</t>
+          <t>1351107909</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1396364412</t>
+          <t>1351365045</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1396365583</t>
+          <t>1352943816</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>139650088X</t>
+          <t>1355824680</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1396586881</t>
+          <t>1358709491</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1397005165</t>
+          <t>1360455698</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1397233788</t>
+          <t>1362327239</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1397658363</t>
+          <t>1362699969</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>139817064X</t>
+          <t>1363224212</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1398298093</t>
+          <t>1364267624</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1398502723</t>
+          <t>1364768488</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1398835250</t>
+          <t>1365165833</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1398963054</t>
+          <t>1368091679</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1399207539</t>
+          <t>136921832X</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1399521926</t>
+          <t>1370535988</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1399522000</t>
+          <t>1371361800</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1399522418</t>
+          <t>1371364222</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1400087805</t>
+          <t>1371736219</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1400088208</t>
+          <t>1371736340</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1400485223</t>
+          <t>1372203400</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1400553547</t>
+          <t>1373302356</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1401393136</t>
+          <t>1373302658</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1401485138</t>
+          <t>1373302755</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1401624456</t>
+          <t>137392604X</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1401900801</t>
+          <t>1374107913</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1401994253</t>
+          <t>1374981893</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1402017464</t>
+          <t>1374982768</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1402018320</t>
+          <t>1375082817</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1402096267</t>
+          <t>1375160958</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1402376502</t>
+          <t>137516113X</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1402376871</t>
+          <t>1376359510</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1402574843</t>
+          <t>1376784661</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1402652119</t>
+          <t>1377899411</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1403177406</t>
+          <t>1378384091</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1403433925</t>
+          <t>1378407288</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1404661735</t>
+          <t>1378408780</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1406899453</t>
+          <t>1378586506</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1406943568</t>
+          <t>1378929403</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1408916169</t>
+          <t>1378929535</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1408940604</t>
+          <t>1378929594</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1409344525</t>
+          <t>1379192838</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1409347095</t>
+          <t>1380078598</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1409350509</t>
+          <t>1380088402</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1380088895</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1380199689</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1380372569</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1380377412</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1380593573</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1380595711</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1380701457</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1380805473</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>138081457X</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1380919452</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1380920884</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1381020747</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1381129552</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1381157858</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1381501214</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1381503187</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1381507476</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1381591477</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1381683576</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1381894968</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>138209017X</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>138209275X</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1382093136</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1382523432</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1382524226</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1382691572</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1382692390</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1382692625</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1382814879</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1382816650</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1382816804</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1382817665</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1382817800</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1382818580</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1382819463</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1382819552</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1382819722</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>138281996X</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1382820089</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1382820380</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1382820682</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1382822111</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1382822448</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>138282260X</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1382823614</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1382823703</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1382823983</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>138293775X</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1382942494</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1382942559</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1382943326</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1383399069</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1383399182</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1383400393</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1383400741</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1383588880</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>138382746X</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1384060855</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>138406219X</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1384164456</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1384164510</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1384165614</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1384166270</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1384493638</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1384720278</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1384720782</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1384721940</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1384724575</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1385906073</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1385908726</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>138590903X</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1386166979</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1386172847</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1386172928</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1386273899</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1386571156</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>138657371X</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1386676357</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>138679855X</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1387419382</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1387543326</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1387543466</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1387661523</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1387758764</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1388212706</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1388213621</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1388213818</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1388314061</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>138845825X</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1388755599</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1388856298</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1388858010</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1389051994</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1389142108</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1389144259</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>138922094X</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1389537544</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1389539202</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1389539512</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1389539687</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1389539776</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1389743144</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1390223914</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1390586413</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1390717976</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1390719278</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1390925188</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1390925234</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1391151216</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1391266862</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>139137214X</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1391373669</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1391374800</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1391484657</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>139172237X</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1391811380</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1391811542</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1391811763</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1391812026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1391812123</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>139181245X</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>139181262X</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1391813243</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1391813286</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1391813383</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1391813480</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>139181357X</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1391813928</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1391813995</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1391935187</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1392209005</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1392240352</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1392240700</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1392241162</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1392632293</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1392632927</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>139263296X</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1392634164</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>139273665X</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1392738067</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1392927463</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>139319897X</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1393199062</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1393498108</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1393498450</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1393498523</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1393499015</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1393499422</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1393499651</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1393500277</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1393608531</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1393610862</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1393890369</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1394119135</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1394781083</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1394785291</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1394849540</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1394978782</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1394986386</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1395213321</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1395276080</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>139527861X</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1395280665</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1395283079</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1395398798</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1395509948</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1395510733</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1395512957</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1395513198</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1395516022</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1395519897</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1395520402</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>139599319X</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1395993203</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1395995540</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1395996369</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1395996431</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1396109072</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1396110089</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1396232052</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1396361790</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1396496521</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1396498281</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1396498567</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1396897763</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1397004940</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1397104546</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1397105402</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1397234024</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1397234032</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1397235411</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1397235950</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1397330686</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1397332182</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1397333200</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1397333367</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1397440783</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1397441046</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1398283169</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1398296090</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1398297836</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1398298654</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1398392936</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>139839503X</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1398395404</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1398395455</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1398397393</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1398503584</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1398594059</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1398836001</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1398957526</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1398959049</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1399059947</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1399060201</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1399060554</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1399194011</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1399277790</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1399420844</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1399521462</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1399663747</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1400086507</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1400086612</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1400087538</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1400553342</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>140090630X</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1400908299</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1401040497</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>140112223X</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1401236286</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1401299466</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1401392202</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1401392628</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1401392814</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1401393284</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1401393829</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1401484565</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1401485073</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1401539149</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1401746365</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1401746918</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1401820425</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1401821790</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1401920810</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>140192252X</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1402015917</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1402016670</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1402103387</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1402115245</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1402118090</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1402180608</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1402264607</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1402376588</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1402476477</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>140251297X</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1402575491</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1402648316</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1402652097</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1402804393</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1402804873</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1402869258</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1402956959</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>1402958803</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1402959400</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1402961340</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1402962584</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1402963386</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1402963645</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1402965761</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1402965923</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1402966253</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1402968892</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1403057001</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1403090068</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>140309666X</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1403177481</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1403178526</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1403178550</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1403304467</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1403304572</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1403305609</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1403306494</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1403306699</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1403306931</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1403308578</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>1403328447</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1403645787</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1403646872</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1403647429</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1403647488</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1403650837</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1403793700</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1403804311</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1403812608</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1403812748</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1403820090</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>1403820252</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1404267689</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>1404273735</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>140427443X</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>1404660674</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1404681558</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>140508426X</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1405084448</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1405084510</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1405092572</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1405102624</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>1405102993</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1405103116</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>140510323X</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1405106301</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1405106743</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>140543872X</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1405441151</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1405765437</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1406082988</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1406086282</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1406087378</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>1406087505</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1406089168</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1406507172</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1406512001</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1406890863</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1406890979</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1406891118</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1406891258</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1406891630</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1406891789</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>1406892114</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>1406892238</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>1406892394</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>1406892580</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>1406892718</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>1406892815</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>140689298X</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1406893080</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>1406893188</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1406893587</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1406893722</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1406898287</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>140689849X</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>1406898678</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>1406898848</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>140689916X</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>1406899259</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1406916242</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1406934755</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>1406939714</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1406940666</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>140694369X</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>1406943827</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1406946222</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>1406952052</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>140695599X</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1406959901</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>1407313541</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>1407737171</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>1407789945</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1408533014</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>1408915936</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1408925079</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>1409351718</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>1409352137</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>1409360202</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1409361462</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>1409373460</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>1409383008</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>1409389189</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>1409747123</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1409747271</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>1409749444</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1409755061</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1409756777</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>1409758311</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>1409758516</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>1409773523</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>1409794202</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>1409795896</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>1409799190</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>140979993X</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>1409803414</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>1410151824</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1410174913</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1410181774</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1410183459</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>141018420X</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>1410184668</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1410193349</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1410193500</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1410588556</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>1411667832</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>1411679989</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1411682521</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1412069580</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>1412069742</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>1412071585</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1412072123</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>1412074533</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>1412077567</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>141208122X</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>1412081394</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1412081661</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>141208184X</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>1412081947</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>1412081963</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1412082056</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1412082110</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1412082137</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>141208217X</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>1412082285</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>1412082307</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>1412082544</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>1412082781</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>1412083826</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>141208735X</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>1412087511</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>1412087546</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>1412087759</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>1412087937</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>1412090512</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>1412459265</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>1412522110</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>1412528089</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>1412530865</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>1412704960</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>1412708818</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>1412951607</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>1412951879</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1412962455</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>1413002234</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>1413381529</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>1413381650</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>1414501269</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>141450232X</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>1414520794</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>1414638418</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>1414638825</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>141463983X</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1414649290</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>1414936044</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>1414939892</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1415080461</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1415081026</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1415081158</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>141508128X</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>1415096740</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>1415097755</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>1415098522</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>1415099235</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>1415099847</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>1415100918</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>1415101264</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>1415102082</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>1415102295</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>1415102724</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>1415355134</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>141536706X</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>1415419221</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>1415419434</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>1415419698</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>1415419868</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>1415420157</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>1415420548</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>1415420734</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>1415420874</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>1415420998</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>1415421250</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>1415421471</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>1415422362</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>1415422605</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>1415423237</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>1415423903</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>1415424454</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>1415425221</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>1415425949</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>1415426414</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>1415426759</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>1415426996</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>1415427402</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>1415428832</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>1415429375</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>1415526176</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>1415526508</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>1415537089</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>1415616981</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>1415619182</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>1415672350</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>1415675074</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>1415675082</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>1415675678</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>1415676143</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>1415676283</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>1415677409</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>1415712107</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>1415712867</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>1415713995</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>1415714010</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>1415716862</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>1415927766</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>1415936854</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>141598168X</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>1415982201</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>997408138</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>998433268</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>999046322</t>
         </is>
       </c>
     </row>
